--- a/astro-site/public/dl/kit-tareas-restaurante-creativo/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-restaurante-creativo/05-tareas-semanales-mensuales.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Semanales" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Mensuales" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semanales" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensuales" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Semanales'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Mensuales'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,6 +83,11 @@
       <name val="Calibri"/>
       <color rgb="00999999"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="10">
@@ -162,63 +170,74 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="8" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="9" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -578,15 +597,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -594,6 +614,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -622,9 +643,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -653,8 +672,25 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-restaurante-creativo · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -663,18 +699,18 @@
   <sheetPr>
     <tabColor rgb="004CAF50"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -691,6 +727,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -849,6 +886,7 @@
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="13" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -988,6 +1026,7 @@
       <c r="F19" s="11" t="n"/>
       <c r="G19" s="13" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
@@ -1127,6 +1166,7 @@
       <c r="F27" s="11" t="n"/>
       <c r="G27" s="13" t="n"/>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
@@ -1227,6 +1267,26 @@
       <c r="E33" s="12" t="n"/>
       <c r="F33" s="11" t="n"/>
       <c r="G33" s="13" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C34">
+        <f>COUNTIF(E6:E33,"✓")</f>
+        <v>3.0</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E34">
+        <f>COUNTIF(B6:B33,"?*")</f>
+        <v>22.0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
@@ -1249,16 +1309,30 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A21:G21"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A21:G21"/>
     <mergeCell ref="A29:G29"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G33">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E23 E24 E25 E26 E27 E31 E32 E33" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E23 E24 E25 E26 E27 E31 E32 E33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1267,18 +1341,18 @@
   <sheetPr>
     <tabColor rgb="004CAF50"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1295,6 +1369,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1415,6 +1490,7 @@
       <c r="F9" s="11" t="n"/>
       <c r="G9" s="13" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -1554,6 +1630,7 @@
       <c r="F17" s="11" t="n"/>
       <c r="G17" s="13" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
@@ -1693,6 +1770,7 @@
       <c r="F25" s="11" t="n"/>
       <c r="G25" s="13" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
@@ -1812,6 +1890,26 @@
       <c r="E32" s="12" t="n"/>
       <c r="F32" s="11" t="n"/>
       <c r="G32" s="13" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C33">
+        <f>COUNTIF(E6:E32,"✓")</f>
+        <v>3.0</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E33">
+        <f>COUNTIF(B6:B32,"?*")</f>
+        <v>21.0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
@@ -1834,15 +1932,29 @@
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A11:G11"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G32">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E13 E14 E15 E16 E17 E21 E22 E23 E24 E25 E29 E30 E31 E32" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16 E17 E21 E22 E23 E24 E25 E29 E30 E31 E32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-restaurante-creativo/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-restaurante-creativo/05-tareas-semanales-mensuales.xlsx
@@ -10,10 +10,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semanales" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensuales" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trimestral y Anual" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Semanales'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Mensuales'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Trimestral y Anual'!$5:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -90,7 +92,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -145,8 +147,13 @@
         <bgColor rgb="00E0F7FA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -168,11 +175,55 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -223,6 +274,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -599,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -674,9 +736,45 @@
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-restaurante-creativo · info@aichef.pro</t>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Más allá del mes:</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>▸ La hoja «Trimestral y Anual» recoge lo que se CONTRATA y se pide por escrito en una inspección: DDD, conductos de extracción, analíticas, instalación de gas, frigorista, calibración de básculas y sondas, extintores, legionela, eléctrica, RGSEAA, carnés de manipulador, póliza y facturación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>▸ Anota en «Notas» el número de parte de cada revisión y la fecha de la siguiente; la columna «Cadencia» ya trae la periodicidad legal o recomendada de cada una.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>▸ Al pie de «Semanales» tienes una tabla editable de vida útil en congelación por familia: ajústala a tu producto y a tu proveedor. Está fuera del contador porque es una referencia, no una tarea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-restaurante-creativo · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -701,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -854,12 +952,12 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Pedido semanal a proveedores premium</t>
+          <t>Revisar el congelador y el arcón: rotación FIFO, etiquetas legibles y descarte de lo que ha superado la vida útil de la tabla del pie de esta hoja</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Proveedores</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="D10" s="11" t="n"/>
@@ -873,12 +971,12 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Registrar mermas de la semana y causas</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>Admin</t>
+          <t>Pedido semanal a proveedores premium</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Proveedores</t>
         </is>
       </c>
       <c r="D11" s="11" t="n"/>
@@ -886,77 +984,77 @@
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="13" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Registrar mermas de la semana y causas</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="13" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>🧪 FERMENTACIONES Y MADURACIONES</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Medir pH de TODAS las fermentaciones activas</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>I+D</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="13" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Verificar estado de koji / cultivos activos</t>
+          <t>Medir pH de TODAS las fermentaciones activas</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -971,16 +1069,16 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Controlar maduraciones en cámara (temp., humedad, día)</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Cámara</t>
+          <t>Verificar estado de koji / cultivos activos</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>I+D</t>
         </is>
       </c>
       <c r="D17" s="11" t="n"/>
@@ -990,16 +1088,16 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Evaluar fermentaciones listas para uso en carta</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>I+D</t>
+          <t>Controlar maduraciones en cámara (temp., humedad, día)</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Cámara</t>
         </is>
       </c>
       <c r="D18" s="11" t="n"/>
@@ -1009,11 +1107,11 @@
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Descartar fermentaciones fuera de parámetros</t>
+          <t>Evaluar fermentaciones listas para uso en carta</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
@@ -1026,77 +1124,77 @@
       <c r="F19" s="11" t="n"/>
       <c r="G19" s="13" t="n"/>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Descartar fermentaciones fuera de parámetros</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>I+D</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="13" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>🔧 MANTENIMIENTO EQUIPAMIENTO</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Mantenimiento Pacojet: limpieza profunda, verificar cuchillas</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="13" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Mantenimiento Roner/sous-vide: calibración, limpieza</t>
+          <t>Mantenimiento Pacojet: limpieza profunda, verificar cuchillas</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -1111,11 +1209,11 @@
     </row>
     <row r="25">
       <c r="A25" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Mantenimiento deshidratador: limpieza bandejas, filtros</t>
+          <t>Mantenimiento Roner/sous-vide: calibración, limpieza</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
@@ -1130,11 +1228,11 @@
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Verificar calibración de básculas de precisión (0,01g)</t>
+          <t>Mantenimiento deshidratador: limpieza bandejas, filtros</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
@@ -1149,11 +1247,11 @@
     </row>
     <row r="27">
       <c r="A27" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Mantenimiento sifones: juntas, válvulas, limpieza</t>
+          <t>Verificar calibración de básculas de precisión (0,01g)</t>
         </is>
       </c>
       <c r="C27" s="16" t="inlineStr">
@@ -1166,101 +1264,101 @@
       <c r="F27" s="11" t="n"/>
       <c r="G27" s="13" t="n"/>
     </row>
-    <row r="28"/>
+    <row r="28">
+      <c r="A28" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Mantenimiento sifones: juntas, válvulas, limpieza</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="11" t="n"/>
+      <c r="G28" s="13" t="n"/>
+    </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Si tu cocina fríe (tempura, crujientes, buñuelos): filtrar o cambiar el aceite SOLO en frío, por debajo de 40 °C — nunca en caliente — y entregarlo a gestor autorizado</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="11" t="n"/>
+      <c r="G29" s="13" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>👥 EQUIPO Y FORMACIÓN</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>Reunión semanal de equipo (feedback, planificación)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Cocina</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="12" t="n"/>
-      <c r="F31" s="11" t="n"/>
-      <c r="G31" s="13" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>Revisión de fichas técnicas actualizadas</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>Fichas</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="11" t="n"/>
-      <c r="G32" s="13" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Actualización de plating bible si hubo cambios</t>
+          <t>Reunión semanal de equipo (feedback, planificación)</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>Emplatado</t>
+          <t>Cocina</t>
         </is>
       </c>
       <c r="D33" s="11" t="n"/>
@@ -1269,58 +1367,349 @@
       <c r="G33" s="13" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="21" t="inlineStr">
+      <c r="A34" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Revisión de fichas técnicas actualizadas</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Fichas</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="11" t="n"/>
+      <c r="G34" s="13" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Actualización de plating bible si hubo cambios</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>Emplatado</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="11" t="n"/>
+      <c r="G35" s="13" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C34">
-        <f>COUNTIF(E6:E33,"✓")</f>
-        <v>3.0</v>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C36">
+        <f>COUNTIFS(B6:B35,"?*",E6:E35,"✓")-COUNTIFS(B6:B35,"Tarea",E6:E35,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E34">
-        <f>COUNTIF(B6:B33,"?*")</f>
-        <v>22.0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="E36">
+        <f>COUNTIF(B6:B35,"?*")-COUNTIF(B6:B35,"Tarea")-COUNTIF(E6:E35,"N/A")</f>
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>Firma responsable: _________________  Fecha: ___/___/______</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="17" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>VIDA ÚTIL ORIENTATIVA EN CONGELACIÓN A −18 °C — ajústala a tu producto y a tu proveedor</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n"/>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Familia</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Vida útil</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+      <c r="E40" s="22" t="n"/>
+      <c r="F40" s="22" t="n"/>
+      <c r="G40" s="23" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="n"/>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>Carnes rojas y aves crudas, en pieza</t>
+        </is>
+      </c>
+      <c r="C41" s="25" t="inlineStr">
+        <is>
+          <t>6-12 meses</t>
+        </is>
+      </c>
+      <c r="D41" s="26" t="inlineStr">
+        <is>
+          <t>Porciona ANTES de congelar: descongelar y volver a congelar no se hace</t>
+        </is>
+      </c>
+      <c r="E41" s="22" t="n"/>
+      <c r="F41" s="22" t="n"/>
+      <c r="G41" s="23" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="n"/>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>Carne picada y preparados de carne</t>
+        </is>
+      </c>
+      <c r="C42" s="25" t="inlineStr">
+        <is>
+          <t>3 meses</t>
+        </is>
+      </c>
+      <c r="D42" s="26" t="inlineStr">
+        <is>
+          <t>Más superficie expuesta, se enrancia antes</t>
+        </is>
+      </c>
+      <c r="E42" s="22" t="n"/>
+      <c r="F42" s="22" t="n"/>
+      <c r="G42" s="23" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="n"/>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>Pescado azul (atún, caballa, sardina)</t>
+        </is>
+      </c>
+      <c r="C43" s="25" t="inlineStr">
+        <is>
+          <t>2-3 meses</t>
+        </is>
+      </c>
+      <c r="D43" s="26" t="inlineStr">
+        <is>
+          <t>La grasa se oxida: envasa al vacío y ponle fecha de entrada</t>
+        </is>
+      </c>
+      <c r="E43" s="22" t="n"/>
+      <c r="F43" s="22" t="n"/>
+      <c r="G43" s="23" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="n"/>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>Pescado blanco y marisco crudo</t>
+        </is>
+      </c>
+      <c r="C44" s="25" t="inlineStr">
+        <is>
+          <t>3-6 meses</t>
+        </is>
+      </c>
+      <c r="D44" s="26" t="inlineStr">
+        <is>
+          <t>Si va a servirse crudo, la congelación cuenta además como tratamiento anti-ANISAKIS: ≥24 h a −20 °C</t>
+        </is>
+      </c>
+      <c r="E44" s="22" t="n"/>
+      <c r="F44" s="22" t="n"/>
+      <c r="G44" s="23" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="n"/>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>Fondos, glacés, caldos y consomés</t>
+        </is>
+      </c>
+      <c r="C45" s="25" t="inlineStr">
+        <is>
+          <t>4-6 meses</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="inlineStr">
+        <is>
+          <t>Congela en porciones de servicio: descongelar un bloque entero para un pase es merma segura</t>
+        </is>
+      </c>
+      <c r="E45" s="22" t="n"/>
+      <c r="F45" s="22" t="n"/>
+      <c r="G45" s="23" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="n"/>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>Sous-vide ya cocinado y abatido, en su bolsa</t>
+        </is>
+      </c>
+      <c r="C46" s="25" t="inlineStr">
+        <is>
+          <t>3 meses</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="inlineStr">
+        <is>
+          <t>Abate primero a ≤ −18 °C; la bolsa intacta o la vida útil no vale</t>
+        </is>
+      </c>
+      <c r="E46" s="22" t="n"/>
+      <c r="F46" s="22" t="n"/>
+      <c r="G46" s="23" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="n"/>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>Purés, cremas y bases de helado</t>
+        </is>
+      </c>
+      <c r="C47" s="25" t="inlineStr">
+        <is>
+          <t>3-4 meses</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr">
+        <is>
+          <t>Las que llevan huevo o lácteo, en el tramo corto</t>
+        </is>
+      </c>
+      <c r="E47" s="22" t="n"/>
+      <c r="F47" s="22" t="n"/>
+      <c r="G47" s="23" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="n"/>
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>Masas crudas, hojaldres y crujientes sin hornear</t>
+        </is>
+      </c>
+      <c r="C48" s="25" t="inlineStr">
+        <is>
+          <t>2-3 meses</t>
+        </is>
+      </c>
+      <c r="D48" s="26" t="inlineStr">
+        <is>
+          <t>Pierden gasificación: rotúlalas con la fecha de elaboración</t>
+        </is>
+      </c>
+      <c r="E48" s="22" t="n"/>
+      <c r="F48" s="22" t="n"/>
+      <c r="G48" s="23" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="n"/>
+      <c r="B49" s="24" t="inlineStr">
+        <is>
+          <t>Frutas y verduras blanqueadas o en puré</t>
+        </is>
+      </c>
+      <c r="C49" s="25" t="inlineStr">
+        <is>
+          <t>8-12 meses</t>
+        </is>
+      </c>
+      <c r="D49" s="26" t="inlineStr">
+        <is>
+          <t>Blanquea antes de congelar: sin blanquear pierden color y textura en pocas semanas</t>
+        </is>
+      </c>
+      <c r="E49" s="22" t="n"/>
+      <c r="F49" s="22" t="n"/>
+      <c r="G49" s="23" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="n"/>
+      <c r="B50" s="24" t="inlineStr">
+        <is>
+          <t>Producto que ya ha salido a un pase o a la mesa</t>
+        </is>
+      </c>
+      <c r="C50" s="25" t="inlineStr">
+        <is>
+          <t>No congelar</t>
+        </is>
+      </c>
+      <c r="D50" s="26" t="inlineStr">
+        <is>
+          <t>Lo que ha salido a sala o ha roto la cadena de frío no vuelve al congelador: se retira y se anota como merma</t>
+        </is>
+      </c>
+      <c r="E50" s="22" t="n"/>
+      <c r="F50" s="22" t="n"/>
+      <c r="G50" s="23" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="20">
+    <mergeCell ref="D44:G44"/>
+    <mergeCell ref="D47:G47"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D49:G49"/>
+    <mergeCell ref="D48:G48"/>
+    <mergeCell ref="D41:G41"/>
+    <mergeCell ref="D46:G46"/>
+    <mergeCell ref="D50:G50"/>
+    <mergeCell ref="D40:G40"/>
+    <mergeCell ref="A37:G37"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="D43:G43"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A22:G22"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G33">
+  <conditionalFormatting sqref="A6:G35">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E23 E24 E25 E26 E27 E31 E32 E33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E16 E17 E18 E19 E20 E24 E25 E26 E27 E28 E29 E33 E34 E35" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1343,7 +1732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1579,7 +1968,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Calibración profesional de básculas y termómetros</t>
+          <t>Verificación interna de las básculas con su pesa patrón y ajuste si hace falta (el contraste de sondas y termómetros y la calibración externa certificada van en «Trimestral y Anual»)</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
@@ -1770,82 +2159,82 @@
       <c r="F25" s="11" t="n"/>
       <c r="G25" s="13" t="n"/>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Archivar los registros de jornada del mes junto a nóminas y contratos: hay que conservarlos 4 años y es lo primero que pide una inspección de Trabajo</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="11" t="n"/>
+      <c r="G26" s="13" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>📚 FORMACIÓN Y DESARROLLO</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>Sesión de formación equipo (técnica nueva o repaso)</t>
-        </is>
-      </c>
-      <c r="C29" s="15" t="inlineStr">
-        <is>
-          <t>I+D</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="12" t="n"/>
-      <c r="F29" s="11" t="n"/>
-      <c r="G29" s="13" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Evaluación de desempeño informal por rol</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="inlineStr">
-        <is>
-          <t>Admin</t>
+          <t>Sesión de formación equipo (técnica nueva o repaso)</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>I+D</t>
         </is>
       </c>
       <c r="D30" s="11" t="n"/>
@@ -1855,16 +2244,16 @@
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Planificación de eventos especiales del próximo mes</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>Eventos</t>
+          <t>Evaluación de desempeño informal por rol</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D31" s="11" t="n"/>
@@ -1874,16 +2263,16 @@
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Revisión de objetivos y KPIs del mes</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="inlineStr">
-        <is>
-          <t>Admin</t>
+          <t>Planificación de eventos especiales del próximo mes</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>Eventos</t>
         </is>
       </c>
       <c r="D32" s="11" t="n"/>
@@ -1892,34 +2281,53 @@
       <c r="G32" s="13" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="21" t="inlineStr">
+      <c r="A33" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Revisión de objetivos y KPIs del mes</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="11" t="n"/>
+      <c r="G33" s="13" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C33">
-        <f>COUNTIF(E6:E32,"✓")</f>
-        <v>3.0</v>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C34">
+        <f>COUNTIFS(B6:B33,"?*",E6:E33,"✓")-COUNTIFS(B6:B33,"Tarea",E6:E33,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E33">
-        <f>COUNTIF(B6:B32,"?*")</f>
-        <v>21.0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="17" t="inlineStr">
-        <is>
-          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
-        </is>
+      <c r="E34">
+        <f>COUNTIF(B6:B33,"?*")-COUNTIF(B6:B33,"Tarea")-COUNTIF(E6:E33,"N/A")</f>
+        <v>19.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
@@ -1928,22 +2336,833 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A36:G36"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A34:G34"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A35:G35"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G32">
+  <conditionalFormatting sqref="A6:G33">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16 E17 E21 E22 E23 E24 E25 E29 E30 E31 E32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16 E17 E21 E22 E23 E24 E25 E26 E30 E31 E32 E33" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="004CAF50"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Mantenimiento Trimestral y Anual — Revisiones Contratadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>AI Chef Pro · aichef.pro — Kit de Tareas: Restaurante Creativo / De Autor</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>🐜 HIGIENE, PLAGAS Y AGUA — empresa autorizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Cadencia</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Control de plagas (DDD): visita de la empresa autorizada, parte firmado y certificado en vigor</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Limpieza de campana y conductos de extracción por empresa homologada, con certificado</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Analítica de superficies y de producto en laboratorio externo (verificación del plan de limpieza)</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Revisar el plan APPCC y las fichas de proveedor: altas, bajas y cambios de carta del año</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Renovar los carnés de manipulador de alimentos de toda la brigada, extras incluidos</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Comprobar que el registro sanitario (RGSEAA) recoge la actividad y las instalaciones actuales</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="n"/>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>🔧 EQUIPOS, FRÍO Y GAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Cadencia</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Revisión de la instalación de gas por empresa habilitada, si la cocina tiene gas</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Cada 5 años</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Revisión de cámaras frigoríficas y de maduración por frigorista: gas, juntas, sondas y desescarche</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Cámara</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Calibración externa certificada de las básculas de precisión (0,01 g)</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Revisión por el SAT de Roner/baños térmicos, abatidor, deshidratador, Pacojet y sifones</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Contraste de sondas y termómetros contra un patrón conocido (agua con hielo, 0 °C) y anotar la desviación</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>Cocina</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Retirada del aceite de fritura usado por gestor autorizado y archivo del documento de entrega</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>🧯 SEGURIDAD DEL LOCAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Cadencia</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Revisión de extintores y BIE por empresa mantenedora (etiqueta y acta)</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Revisión del sistema de detección y de las luces de emergencia</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Plan de prevención de legionela si hay torre de refrigeración, spa o agua caliente sanitaria de riesgo</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Revisión de la instalación eléctrica por instalador autorizado (local de pública concurrencia)</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>Cada 5 años</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Simulacro y repaso del plan de emergencia con la brigada y con sala</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="n"/>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>📄 DOCUMENTACIÓN, SEGUROS Y FISCAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Cadencia</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Revisar la póliza de responsabilidad civil: suma asegurada, aforo y actividades cubiertas (chef's table, pop-ups, showcookings)</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Archivar los registros de jornada del trimestre y revisar contratos, altas y horas extra</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Revisión del TPV y del software de facturación (requisitos antifraude / Verifactu)</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Actualizar escandallos y precios de carta con los precios reales de proveedor</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>Food cost</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Renovar licencias, tasa de terraza y seguros del local</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Anotar en «Notas» el nº de parte de cada revisión y la fecha de la siguiente</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G37" s="13" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C38">
+        <f>COUNTIFS(B6:B37,"?*",E6:E37,"✓")-COUNTIFS(B6:B37,"Tarea",E6:E37,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E38">
+        <f>COUNTIF(B6:B37,"?*")-COUNTIF(B6:B37,"Tarea")-COUNTIF(E6:E37,"N/A")</f>
+        <v>23.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>© 2026 AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A13:G13"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A6:G37">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20 E24 E25 E26 E27 E28 E32 E33 E34 E35 E36 E37" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>

--- a/astro-site/public/dl/kit-tareas-restaurante-creativo/05-tareas-semanales-mensuales.xlsx
+++ b/astro-site/public/dl/kit-tareas-restaurante-creativo/05-tareas-semanales-mensuales.xlsx
@@ -661,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1682,24 +1682,24 @@
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="D44:G44"/>
-    <mergeCell ref="D47:G47"/>
     <mergeCell ref="A31:G31"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D49:G49"/>
     <mergeCell ref="D48:G48"/>
     <mergeCell ref="D41:G41"/>
-    <mergeCell ref="D46:G46"/>
     <mergeCell ref="D50:G50"/>
-    <mergeCell ref="D40:G40"/>
     <mergeCell ref="A37:G37"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D42:G42"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A39:G39"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="D47:G47"/>
+    <mergeCell ref="D49:G49"/>
+    <mergeCell ref="D46:G46"/>
+    <mergeCell ref="D40:G40"/>
+    <mergeCell ref="D42:G42"/>
     <mergeCell ref="D43:G43"/>
-    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
   <conditionalFormatting sqref="A6:G35">
@@ -2374,7 +2374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3143,17 +3143,16 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A4:G4"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A4:G4"/>
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A22:G22"/>
     <mergeCell ref="A39:G39"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A22:G22"/>
   </mergeCells>
   <conditionalFormatting sqref="A6:G37">
     <cfRule type="expression" priority="1" dxfId="0">
